--- a/Design/Excel/ET/Datas/Game/Entity.xlsx
+++ b/Design/Excel/ET/Datas/Game/Entity.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0" fullPrecision="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -86,100 +86,49 @@
     <t>加载优先级</t>
   </si>
   <si>
-    <t>PlayerShip</t>
-  </si>
-  <si>
-    <t>玩家战机</t>
+    <t>SurvivorPlayer</t>
+  </si>
+  <si>
+    <t>联机幸存者玩家</t>
+  </si>
+  <si>
+    <t>SurvivorOnline/Player</t>
   </si>
   <si>
     <t>Aircraft</t>
   </si>
   <si>
-    <t>EnemyShip</t>
-  </si>
-  <si>
-    <t>敌人战机</t>
-  </si>
-  <si>
-    <t>PlayerEngine</t>
-  </si>
-  <si>
-    <t>玩家推进器</t>
-  </si>
-  <si>
-    <t>EnemyEngine</t>
-  </si>
-  <si>
-    <t>敌人推进器</t>
-  </si>
-  <si>
-    <t>DefaultWeapon</t>
-  </si>
-  <si>
-    <t>默认武器</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>DefaultArmor</t>
-  </si>
-  <si>
-    <t>默认装甲</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>PlayerBolt</t>
-  </si>
-  <si>
-    <t>玩家子弹</t>
+    <t>SurvivorMonster</t>
+  </si>
+  <si>
+    <t>联机幸存者怪物</t>
+  </si>
+  <si>
+    <t>SurvivorOnline/Monster</t>
+  </si>
+  <si>
+    <t>SurvivorProjectile</t>
+  </si>
+  <si>
+    <t>联机幸存者投射物</t>
+  </si>
+  <si>
+    <t>SurvivorOnline/Projectile</t>
   </si>
   <si>
     <t>Bullet</t>
   </si>
   <si>
-    <t>EnemyBolt</t>
-  </si>
-  <si>
-    <t>敌人子弹</t>
-  </si>
-  <si>
-    <t>Asteroid01</t>
-  </si>
-  <si>
-    <t>小行星</t>
-  </si>
-  <si>
-    <t>Asteroid</t>
-  </si>
-  <si>
-    <t>Asteroid02</t>
-  </si>
-  <si>
-    <t>Asteroid03</t>
-  </si>
-  <si>
-    <t>PlayerExplosion</t>
-  </si>
-  <si>
-    <t>玩家死亡特效</t>
+    <t>SurvivorPickup</t>
+  </si>
+  <si>
+    <t>联机幸存者经验拾取物</t>
+  </si>
+  <si>
+    <t>SurvivorOnline/Pickup</t>
   </si>
   <si>
     <t>Effect</t>
-  </si>
-  <si>
-    <t>EnemyExplosion</t>
-  </si>
-  <si>
-    <t>敌人死亡特效</t>
-  </si>
-  <si>
-    <t>AsteroidExplosion</t>
-  </si>
-  <si>
-    <t>小行星死亡特效</t>
   </si>
 </sst>
 </file>
@@ -192,7 +141,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,7 +154,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -213,14 +162,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -236,7 +185,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -267,7 +216,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,7 +224,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -283,7 +232,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,14 +240,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -306,42 +255,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -647,149 +589,149 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1152,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.87272727272727" style="1"/>
     <col min="2" max="2" width="19.3727272727273" style="1" customWidth="1"/>
@@ -1236,7 +1178,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="B4" s="3">
-        <v>10000</v>
+        <v>81001</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>19</v>
@@ -1245,278 +1187,78 @@
         <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="B5" s="3">
-        <v>10001</v>
+        <v>81002</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G5" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" s="3">
+        <v>81003</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="3">
-        <v>20000</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+    <row r="7" spans="1:7">
       <c r="B7" s="3">
-        <v>20001</v>
+        <v>81004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="3">
-        <v>30000</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="3">
-        <v>40000</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="3">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="3">
-        <v>50001</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="3">
-        <v>60000</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="3">
-        <v>60001</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="3">
-        <v>60002</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="3">
-        <v>70000</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="3">
-        <v>70001</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3">
-        <v>70002</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>